--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/127.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/127.xlsx
@@ -426,13 +426,13 @@
         <v>-18.84521057672834</v>
       </c>
       <c r="E2">
-        <v>-5.315936958045765</v>
+        <v>-4.540290873063971</v>
       </c>
       <c r="F2">
-        <v>-1.269275212458556</v>
+        <v>-1.115880624900922</v>
       </c>
       <c r="G2">
-        <v>-9.22482305366534</v>
+        <v>-9.193372871042262</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.96355935832227</v>
       </c>
       <c r="E3">
-        <v>-5.212560953398667</v>
+        <v>-4.441207861776144</v>
       </c>
       <c r="F3">
-        <v>-0.7770847532346226</v>
+        <v>-1.137599567825258</v>
       </c>
       <c r="G3">
-        <v>-8.9132146442359</v>
+        <v>-8.533147463599871</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.10573541542488</v>
       </c>
       <c r="E4">
-        <v>-6.189298455165071</v>
+        <v>-5.594075831596879</v>
       </c>
       <c r="F4">
-        <v>-0.9326379319550004</v>
+        <v>-1.003457301228664</v>
       </c>
       <c r="G4">
-        <v>-8.382107133916163</v>
+        <v>-8.338378137887929</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.18449752013072</v>
       </c>
       <c r="E5">
-        <v>-7.063475077605757</v>
+        <v>-5.848422102711692</v>
       </c>
       <c r="F5">
-        <v>-0.9503999856496116</v>
+        <v>-0.7132709070779054</v>
       </c>
       <c r="G5">
-        <v>-8.196875489902862</v>
+        <v>-7.699770592816978</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-19.14188023471418</v>
       </c>
       <c r="E6">
-        <v>-8.561684475251433</v>
+        <v>-8.206253607337402</v>
       </c>
       <c r="F6">
-        <v>-0.6882926973795944</v>
+        <v>-0.2296649257686117</v>
       </c>
       <c r="G6">
-        <v>-8.247199092645323</v>
+        <v>-7.558592378294758</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.90833788723702</v>
       </c>
       <c r="E7">
-        <v>-8.886711168677966</v>
+        <v>-8.356897823676563</v>
       </c>
       <c r="F7">
-        <v>-0.5281523144751461</v>
+        <v>-0.5328408758378046</v>
       </c>
       <c r="G7">
-        <v>-8.022144896340128</v>
+        <v>-8.035771101779767</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-18.45407862408315</v>
       </c>
       <c r="E8">
-        <v>-9.568500101376783</v>
+        <v>-9.470689591285112</v>
       </c>
       <c r="F8">
-        <v>-0.3904601710690943</v>
+        <v>-0.1563686404432009</v>
       </c>
       <c r="G8">
-        <v>-8.018903872257182</v>
+        <v>-7.295046469004458</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.77737030496772</v>
       </c>
       <c r="E9">
-        <v>-10.31321670888619</v>
+        <v>-9.210320449740097</v>
       </c>
       <c r="F9">
-        <v>-0.4911577361434384</v>
+        <v>-0.2541284310444049</v>
       </c>
       <c r="G9">
-        <v>-6.829408307269348</v>
+        <v>-6.113979552959608</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.90097702905831</v>
       </c>
       <c r="E10">
-        <v>-11.34406041809624</v>
+        <v>-11.72133664462327</v>
       </c>
       <c r="F10">
-        <v>0.1104406706897559</v>
+        <v>-0.4929552423574621</v>
       </c>
       <c r="G10">
-        <v>-6.428186740637376</v>
+        <v>-6.045414844295763</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.88825573894313</v>
       </c>
       <c r="E11">
-        <v>-11.89494022418132</v>
+        <v>-11.2767355950242</v>
       </c>
       <c r="F11">
-        <v>-0.03576310015882525</v>
+        <v>0.07361396518508474</v>
       </c>
       <c r="G11">
-        <v>-5.542331101965956</v>
+        <v>-6.194445672837134</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.82436796733252</v>
       </c>
       <c r="E12">
-        <v>-12.10130731318487</v>
+        <v>-12.31016959136664</v>
       </c>
       <c r="F12">
-        <v>-0.2965186954300149</v>
+        <v>-0.005446217819567912</v>
       </c>
       <c r="G12">
-        <v>-4.957056445532664</v>
+        <v>-5.091464594427074</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-13.78923617635975</v>
       </c>
       <c r="E13">
-        <v>-13.027701769408</v>
+        <v>-12.09679695307323</v>
       </c>
       <c r="F13">
-        <v>0.03694404656604205</v>
+        <v>-0.1109416199647358</v>
       </c>
       <c r="G13">
-        <v>-4.558731606247554</v>
+        <v>-4.305458319765612</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.87004556760776</v>
       </c>
       <c r="E14">
-        <v>-14.22553295765089</v>
+        <v>-13.41917023347507</v>
       </c>
       <c r="F14">
-        <v>0.4278311732029756</v>
+        <v>0.2872725220899783</v>
       </c>
       <c r="G14">
-        <v>-3.990082509512482</v>
+        <v>-4.272918967660115</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.13328228290529</v>
       </c>
       <c r="E15">
-        <v>-14.55436356924387</v>
+        <v>-15.16616946462815</v>
       </c>
       <c r="F15">
-        <v>0.3473123970502032</v>
+        <v>0.6093072422002241</v>
       </c>
       <c r="G15">
-        <v>-3.29751307215141</v>
+        <v>-3.06662569460602</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-11.60123920222584</v>
       </c>
       <c r="E16">
-        <v>-15.60498312444542</v>
+        <v>-14.99676830894922</v>
       </c>
       <c r="F16">
-        <v>0.7459493885843397</v>
+        <v>0.8835987719306747</v>
       </c>
       <c r="G16">
-        <v>-2.556808302649336</v>
+        <v>-1.903511867020638</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.26978792933251</v>
       </c>
       <c r="E17">
-        <v>-16.07431869907438</v>
+        <v>-16.9584307934879</v>
       </c>
       <c r="F17">
-        <v>0.5625530761646208</v>
+        <v>0.7288992106987185</v>
       </c>
       <c r="G17">
-        <v>-2.2378239977584</v>
+        <v>-2.315095441190528</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.10375705828012</v>
       </c>
       <c r="E18">
-        <v>-17.83632076461487</v>
+        <v>-17.07239437036493</v>
       </c>
       <c r="F18">
-        <v>1.091610625394069</v>
+        <v>0.8461805522665868</v>
       </c>
       <c r="G18">
-        <v>-1.209118319067428</v>
+        <v>-1.233483934236464</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.04015122426859</v>
       </c>
       <c r="E19">
-        <v>-18.48765570961211</v>
+        <v>-18.60171891291731</v>
       </c>
       <c r="F19">
-        <v>1.193998796533145</v>
+        <v>1.80973732163234</v>
       </c>
       <c r="G19">
-        <v>-0.6863666256888113</v>
+        <v>-0.8449715519297546</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.02127928383653</v>
       </c>
       <c r="E20">
-        <v>-19.30504979647061</v>
+        <v>-18.69308540449606</v>
       </c>
       <c r="F20">
-        <v>1.235072209450067</v>
+        <v>1.694193305453709</v>
       </c>
       <c r="G20">
-        <v>-0.1130132437424344</v>
+        <v>-1.271876330855392</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.99950560191702</v>
       </c>
       <c r="E21">
-        <v>-19.32329501824752</v>
+        <v>-18.16900057911436</v>
       </c>
       <c r="F21">
-        <v>1.592582733919114</v>
+        <v>1.629283534803508</v>
       </c>
       <c r="G21">
-        <v>-0.7972169325257678</v>
+        <v>-0.778505729137807</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.93740503162677</v>
       </c>
       <c r="E22">
-        <v>-20.60178285704103</v>
+        <v>-20.98379133890607</v>
       </c>
       <c r="F22">
-        <v>1.905329810688265</v>
+        <v>2.201560418465298</v>
       </c>
       <c r="G22">
-        <v>-0.3421990008806394</v>
+        <v>0.8136680425192777</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.82140272944206</v>
       </c>
       <c r="E23">
-        <v>-20.99062027770964</v>
+        <v>-21.32769724047058</v>
       </c>
       <c r="F23">
-        <v>2.226535460751778</v>
+        <v>2.287313342668598</v>
       </c>
       <c r="G23">
-        <v>0.3058767044326274</v>
+        <v>0.6333194531764013</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.65463671150665</v>
       </c>
       <c r="E24">
-        <v>-22.14528152323741</v>
+        <v>-20.82283125877744</v>
       </c>
       <c r="F24">
-        <v>1.702051654206119</v>
+        <v>2.454684134929985</v>
       </c>
       <c r="G24">
-        <v>0.7699324253999661</v>
+        <v>-0.3161880445785857</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.44560464542032</v>
       </c>
       <c r="E25">
-        <v>-21.55262201595756</v>
+        <v>-21.54893583811532</v>
       </c>
       <c r="F25">
-        <v>2.010389693706687</v>
+        <v>2.093876334744993</v>
       </c>
       <c r="G25">
-        <v>0.3256042453011444</v>
+        <v>-0.2231981309259974</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.21422184520587</v>
       </c>
       <c r="E26">
-        <v>-21.02869115869213</v>
+        <v>-21.84140733190071</v>
       </c>
       <c r="F26">
-        <v>1.899409917976352</v>
+        <v>1.766145816309869</v>
       </c>
       <c r="G26">
-        <v>-0.1112884495164741</v>
+        <v>0.8578538938319302</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.986918725500534</v>
       </c>
       <c r="E27">
-        <v>-22.17462150633311</v>
+        <v>-21.49557230040893</v>
       </c>
       <c r="F27">
-        <v>1.916913035753789</v>
+        <v>1.805671948547407</v>
       </c>
       <c r="G27">
-        <v>0.6651106219900225</v>
+        <v>0.2122114394900277</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.787371596805308</v>
       </c>
       <c r="E28">
-        <v>-21.74784000195422</v>
+        <v>-22.34601971904943</v>
       </c>
       <c r="F28">
-        <v>1.9860908938461</v>
+        <v>2.330646703926852</v>
       </c>
       <c r="G28">
-        <v>0.2442641414012514</v>
+        <v>-0.3853652041671964</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.632943430658736</v>
       </c>
       <c r="E29">
-        <v>-21.91780268841011</v>
+        <v>-22.2313497002272</v>
       </c>
       <c r="F29">
-        <v>2.133529163455766</v>
+        <v>1.887994565737865</v>
       </c>
       <c r="G29">
-        <v>-0.1611585075200553</v>
+        <v>-0.6295576642349178</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.534851171485826</v>
       </c>
       <c r="E30">
-        <v>-22.48404307832921</v>
+        <v>-21.65307262639571</v>
       </c>
       <c r="F30">
-        <v>1.903768276655642</v>
+        <v>2.072949244778376</v>
       </c>
       <c r="G30">
-        <v>-0.1879110260229058</v>
+        <v>0.07385380976726699</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.495683274282529</v>
       </c>
       <c r="E31">
-        <v>-20.88856205899878</v>
+        <v>-21.19537975844046</v>
       </c>
       <c r="F31">
-        <v>2.002251029007244</v>
+        <v>2.612242285339309</v>
       </c>
       <c r="G31">
-        <v>0.1596797028728725</v>
+        <v>-1.741026981407669</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.509593254937759</v>
       </c>
       <c r="E32">
-        <v>-21.44381637097527</v>
+        <v>-21.07214639526973</v>
       </c>
       <c r="F32">
-        <v>1.82332551838681</v>
+        <v>1.893901788802454</v>
       </c>
       <c r="G32">
-        <v>-0.02501894330860627</v>
+        <v>-0.4450278558759418</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.567342738755437</v>
       </c>
       <c r="E33">
-        <v>-20.33352964224866</v>
+        <v>-21.37997847288914</v>
       </c>
       <c r="F33">
-        <v>1.996769822833908</v>
+        <v>2.346466342316177</v>
       </c>
       <c r="G33">
-        <v>-1.055661291140052</v>
+        <v>-0.7578975831558439</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.654696017350771</v>
       </c>
       <c r="E34">
-        <v>-20.11934640710787</v>
+        <v>-21.14497331426109</v>
       </c>
       <c r="F34">
-        <v>1.91286033231618</v>
+        <v>2.338364102852789</v>
       </c>
       <c r="G34">
-        <v>-0.6490336036424501</v>
+        <v>-0.7787639516898701</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.752149231891693</v>
       </c>
       <c r="E35">
-        <v>-19.31682382889056</v>
+        <v>-19.33204403003034</v>
       </c>
       <c r="F35">
-        <v>2.24555418509029</v>
+        <v>1.883484171290693</v>
       </c>
       <c r="G35">
-        <v>-1.389791341873153</v>
+        <v>-1.46516253216574</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.843263790540641</v>
       </c>
       <c r="E36">
-        <v>-19.52361206597681</v>
+        <v>-19.13714303721421</v>
       </c>
       <c r="F36">
-        <v>2.426972448821626</v>
+        <v>2.391090423895514</v>
       </c>
       <c r="G36">
-        <v>-0.8452264639362785</v>
+        <v>-0.8838472881974162</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.915412892974382</v>
       </c>
       <c r="E37">
-        <v>-17.68055484417303</v>
+        <v>-18.6792916726687</v>
       </c>
       <c r="F37">
-        <v>2.447359495071078</v>
+        <v>2.013924525309948</v>
       </c>
       <c r="G37">
-        <v>-1.651877300580635</v>
+        <v>-0.952733119778571</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.955979495451484</v>
       </c>
       <c r="E38">
-        <v>-17.5767441060212</v>
+        <v>-17.7061588362124</v>
       </c>
       <c r="F38">
-        <v>2.413967055844037</v>
+        <v>2.527331892683023</v>
       </c>
       <c r="G38">
-        <v>-2.213782816052212</v>
+        <v>-1.198666926799949</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.96085793018721</v>
       </c>
       <c r="E39">
-        <v>-16.87564576015367</v>
+        <v>-16.74507174061651</v>
       </c>
       <c r="F39">
-        <v>2.336789899172842</v>
+        <v>2.975124740273527</v>
       </c>
       <c r="G39">
-        <v>-2.100727685886101</v>
+        <v>-2.224734100696121</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.937256292138231</v>
       </c>
       <c r="E40">
-        <v>-17.47700899447626</v>
+        <v>-17.91897447220287</v>
       </c>
       <c r="F40">
-        <v>2.921874212572791</v>
+        <v>2.779312173476763</v>
       </c>
       <c r="G40">
-        <v>-1.642233681424738</v>
+        <v>-1.266337788168191</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.893502468936312</v>
       </c>
       <c r="E41">
-        <v>-16.6053819029019</v>
+        <v>-16.47777403383975</v>
       </c>
       <c r="F41">
-        <v>2.723564141547379</v>
+        <v>2.244805092192288</v>
       </c>
       <c r="G41">
-        <v>-2.678537062128337</v>
+        <v>-1.423952861292892</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.842941587225804</v>
       </c>
       <c r="E42">
-        <v>-15.49465591219654</v>
+        <v>-14.78631653639075</v>
       </c>
       <c r="F42">
-        <v>2.608636186969854</v>
+        <v>2.79629425200802</v>
       </c>
       <c r="G42">
-        <v>-2.217493937601736</v>
+        <v>-1.276580616066696</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.806472789972027</v>
       </c>
       <c r="E43">
-        <v>-14.30140753964941</v>
+        <v>-15.6439370578594</v>
       </c>
       <c r="F43">
-        <v>2.430276059361232</v>
+        <v>2.421145994758724</v>
       </c>
       <c r="G43">
-        <v>-2.401156383029422</v>
+        <v>-1.599868630158685</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.795790925401196</v>
       </c>
       <c r="E44">
-        <v>-13.3296830586095</v>
+        <v>-15.01330176755122</v>
       </c>
       <c r="F44">
-        <v>3.022483881968828</v>
+        <v>2.181390339926261</v>
       </c>
       <c r="G44">
-        <v>-2.553034280734567</v>
+        <v>-1.82751167307559</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.82079653249178</v>
       </c>
       <c r="E45">
-        <v>-12.91864705835528</v>
+        <v>-13.18932300674176</v>
       </c>
       <c r="F45">
-        <v>2.801309848642217</v>
+        <v>2.259378354026162</v>
       </c>
       <c r="G45">
-        <v>-2.745112132923081</v>
+        <v>-2.127652352756994</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.893967761530085</v>
       </c>
       <c r="E46">
-        <v>-13.28466549849925</v>
+        <v>-13.17649836835203</v>
       </c>
       <c r="F46">
-        <v>2.741352326389595</v>
+        <v>2.284025569188146</v>
       </c>
       <c r="G46">
-        <v>-2.186093413161748</v>
+        <v>-1.771358199638472</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.01535533990312</v>
       </c>
       <c r="E47">
-        <v>-12.45455998510121</v>
+        <v>-12.37274404520463</v>
       </c>
       <c r="F47">
-        <v>2.589012486971644</v>
+        <v>2.562265277765787</v>
       </c>
       <c r="G47">
-        <v>-2.789205288960634</v>
+        <v>-2.909477408402356</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.18269257263311</v>
       </c>
       <c r="E48">
-        <v>-11.22382943319259</v>
+        <v>-12.66137992150552</v>
       </c>
       <c r="F48">
-        <v>2.78589405526133</v>
+        <v>2.691585951702826</v>
       </c>
       <c r="G48">
-        <v>-1.954610137419289</v>
+        <v>-1.04558399051851</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.39816502092575</v>
       </c>
       <c r="E49">
-        <v>-10.54733881508275</v>
+        <v>-11.92761769262067</v>
       </c>
       <c r="F49">
-        <v>2.76497488382429</v>
+        <v>2.567665714937435</v>
       </c>
       <c r="G49">
-        <v>-1.586590032000668</v>
+        <v>-1.578545406340239</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.65391183256559</v>
       </c>
       <c r="E50">
-        <v>-10.55304469233241</v>
+        <v>-11.36258187678761</v>
       </c>
       <c r="F50">
-        <v>2.829816555120127</v>
+        <v>2.538162857438714</v>
       </c>
       <c r="G50">
-        <v>-2.269505918569225</v>
+        <v>-1.972708889882484</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.94339026885856</v>
       </c>
       <c r="E51">
-        <v>-9.134482095533642</v>
+        <v>-11.44548012197202</v>
       </c>
       <c r="F51">
-        <v>2.911230125115123</v>
+        <v>2.764813345820915</v>
       </c>
       <c r="G51">
-        <v>-2.713337516837156</v>
+        <v>-1.022946480120974</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.26808614712019</v>
       </c>
       <c r="E52">
-        <v>-8.646294483610745</v>
+        <v>-10.29878899069775</v>
       </c>
       <c r="F52">
-        <v>2.540072806772734</v>
+        <v>2.547576405400086</v>
       </c>
       <c r="G52">
-        <v>-2.062980845647331</v>
+        <v>-1.976065783059305</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.62148856750598</v>
       </c>
       <c r="E53">
-        <v>-8.942809904684985</v>
+        <v>-10.7594978223421</v>
       </c>
       <c r="F53">
-        <v>2.715870498210174</v>
+        <v>2.465605370922856</v>
       </c>
       <c r="G53">
-        <v>-2.321713221723531</v>
+        <v>-2.056134637472118</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.99923098881174</v>
       </c>
       <c r="E54">
-        <v>-8.170591874526998</v>
+        <v>-9.531629266006332</v>
       </c>
       <c r="F54">
-        <v>2.523652943841458</v>
+        <v>2.223558093630752</v>
       </c>
       <c r="G54">
-        <v>-3.331075382828542</v>
+        <v>-1.801510648410154</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.40506121964976</v>
       </c>
       <c r="E55">
-        <v>-6.929581686620967</v>
+        <v>-8.217583849304592</v>
       </c>
       <c r="F55">
-        <v>2.582633319544254</v>
+        <v>2.43268012494087</v>
       </c>
       <c r="G55">
-        <v>-3.157361126746364</v>
+        <v>-1.814547576743804</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.83226709936541</v>
       </c>
       <c r="E56">
-        <v>-6.771180194306665</v>
+        <v>-8.263380306944164</v>
       </c>
       <c r="F56">
-        <v>2.609133470627302</v>
+        <v>2.293632329271202</v>
       </c>
       <c r="G56">
-        <v>-3.111099563380589</v>
+        <v>-2.334568070052522</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.27342218442729</v>
       </c>
       <c r="E57">
-        <v>-7.252810575866454</v>
+        <v>-8.154792028714237</v>
       </c>
       <c r="F57">
-        <v>2.965085628475557</v>
+        <v>2.54452935521878</v>
       </c>
       <c r="G57">
-        <v>-2.88061276184545</v>
+        <v>-2.0734818960979</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.72752278360903</v>
       </c>
       <c r="E58">
-        <v>-6.287353502853157</v>
+        <v>-7.580631337755719</v>
       </c>
       <c r="F58">
-        <v>2.737201433185228</v>
+        <v>2.549294726318338</v>
       </c>
       <c r="G58">
-        <v>-3.150455328751445</v>
+        <v>-2.248291942753575</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.18360294231074</v>
       </c>
       <c r="E59">
-        <v>-6.126565504736813</v>
+        <v>-6.807000423707338</v>
       </c>
       <c r="F59">
-        <v>2.722575909056145</v>
+        <v>2.311477527526373</v>
       </c>
       <c r="G59">
-        <v>-2.877378358853583</v>
+        <v>-2.432616497289116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.63276241109278</v>
       </c>
       <c r="E60">
-        <v>-6.14188986077877</v>
+        <v>-5.590801744889333</v>
       </c>
       <c r="F60">
-        <v>2.400703518802231</v>
+        <v>2.21762078015377</v>
       </c>
       <c r="G60">
-        <v>-3.578296992064696</v>
+        <v>-2.986129779818641</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.07536242460628</v>
       </c>
       <c r="E61">
-        <v>-5.482738769644295</v>
+        <v>-5.235601829149694</v>
       </c>
       <c r="F61">
-        <v>2.777967607154555</v>
+        <v>2.559527050237992</v>
       </c>
       <c r="G61">
-        <v>-3.835589280831313</v>
+        <v>-2.234751811497956</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.50430006989102</v>
       </c>
       <c r="E62">
-        <v>-5.45522376157369</v>
+        <v>-6.928757504351571</v>
       </c>
       <c r="F62">
-        <v>2.542521216118003</v>
+        <v>2.221174616228016</v>
       </c>
       <c r="G62">
-        <v>-3.857531576665603</v>
+        <v>-3.105657026514027</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.91597260630928</v>
       </c>
       <c r="E63">
-        <v>-5.070466495985986</v>
+        <v>-5.367099657384426</v>
       </c>
       <c r="F63">
-        <v>2.35410138853451</v>
+        <v>1.831036582489085</v>
       </c>
       <c r="G63">
-        <v>-3.65972317014861</v>
+        <v>-3.665579525207581</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.31399473442654</v>
       </c>
       <c r="E64">
-        <v>-4.124613186951894</v>
+        <v>-4.782378565040021</v>
       </c>
       <c r="F64">
-        <v>2.491179054045372</v>
+        <v>1.95886540545378</v>
       </c>
       <c r="G64">
-        <v>-3.690623802212167</v>
+        <v>-3.639651332544009</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.69318008968832</v>
       </c>
       <c r="E65">
-        <v>-4.575812223180137</v>
+        <v>-5.482077612439175</v>
       </c>
       <c r="F65">
-        <v>2.279249112147181</v>
+        <v>2.466766227358873</v>
       </c>
       <c r="G65">
-        <v>-3.737934808513892</v>
+        <v>-3.740056868204565</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.04934975508726</v>
       </c>
       <c r="E66">
-        <v>-3.608706785628049</v>
+        <v>-3.884549722857273</v>
       </c>
       <c r="F66">
-        <v>2.609160393627864</v>
+        <v>1.957094822240319</v>
       </c>
       <c r="G66">
-        <v>-4.01916234152944</v>
+        <v>-3.331562033022815</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.38103130042827</v>
       </c>
       <c r="E67">
-        <v>-4.274596246085936</v>
+        <v>-4.570984869887961</v>
       </c>
       <c r="F67">
-        <v>2.475392673480271</v>
+        <v>1.910198122672326</v>
       </c>
       <c r="G67">
-        <v>-3.52499389833689</v>
+        <v>-2.588672303464821</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.67598614867318</v>
       </c>
       <c r="E68">
-        <v>-4.756706645890538</v>
+        <v>-4.649173502104397</v>
       </c>
       <c r="F68">
-        <v>2.209789354401922</v>
+        <v>1.59590376522379</v>
       </c>
       <c r="G68">
-        <v>-3.515065572264616</v>
+        <v>-3.521411888063399</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.92126500569738</v>
       </c>
       <c r="E69">
-        <v>-4.229411132437401</v>
+        <v>-4.680116564998809</v>
       </c>
       <c r="F69">
-        <v>1.948884890774681</v>
+        <v>1.927319567324142</v>
       </c>
       <c r="G69">
-        <v>-3.84505413052809</v>
+        <v>-3.591519310948545</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-18.10748763593926</v>
       </c>
       <c r="E70">
-        <v>-3.854054978889621</v>
+        <v>-4.309270771562668</v>
       </c>
       <c r="F70">
-        <v>2.013105749351666</v>
+        <v>1.526634052188384</v>
       </c>
       <c r="G70">
-        <v>-3.439078620501725</v>
+        <v>-3.009270493138147</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-18.22003879982405</v>
       </c>
       <c r="E71">
-        <v>-3.699312493573517</v>
+        <v>-6.279872463792485</v>
       </c>
       <c r="F71">
-        <v>1.764373649390492</v>
+        <v>1.507780033265078</v>
       </c>
       <c r="G71">
-        <v>-3.468744419079134</v>
+        <v>-2.635019941014618</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-18.24915079493167</v>
       </c>
       <c r="E72">
-        <v>-3.730355182896097</v>
+        <v>-4.63155773821456</v>
       </c>
       <c r="F72">
-        <v>1.656516941725404</v>
+        <v>1.731684375589907</v>
       </c>
       <c r="G72">
-        <v>-3.529211533353922</v>
+        <v>-2.652641974920158</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.19354762754755</v>
       </c>
       <c r="E73">
-        <v>-4.989968342025638</v>
+        <v>-6.286126286397078</v>
       </c>
       <c r="F73">
-        <v>1.664093390824867</v>
+        <v>1.624271105581142</v>
       </c>
       <c r="G73">
-        <v>-3.080930561881211</v>
+        <v>-2.856651033232206</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.05173092387906</v>
       </c>
       <c r="E74">
-        <v>-4.017818184429004</v>
+        <v>-3.796131267857509</v>
       </c>
       <c r="F74">
-        <v>1.691583358105065</v>
+        <v>1.653552244251702</v>
       </c>
       <c r="G74">
-        <v>-3.006062574510593</v>
+        <v>-2.579770246509721</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.82898621055896</v>
       </c>
       <c r="E75">
-        <v>-5.297007936693704</v>
+        <v>-7.351481496019583</v>
       </c>
       <c r="F75">
-        <v>1.738752455090513</v>
+        <v>1.627877203950597</v>
       </c>
       <c r="G75">
-        <v>-3.031527290798667</v>
+        <v>-2.555871418261722</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.540132138624</v>
       </c>
       <c r="E76">
-        <v>-5.554678107730147</v>
+        <v>-5.896297129920783</v>
       </c>
       <c r="F76">
-        <v>1.231000501541472</v>
+        <v>1.269806047587485</v>
       </c>
       <c r="G76">
-        <v>-2.931926217704154</v>
+        <v>-2.758185477257663</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.20029608931645</v>
       </c>
       <c r="E77">
-        <v>-5.072689976723752</v>
+        <v>-5.21031935876487</v>
       </c>
       <c r="F77">
-        <v>1.233708638656873</v>
+        <v>1.553541215691701</v>
       </c>
       <c r="G77">
-        <v>-2.990933381396124</v>
+        <v>-2.278315280249226</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.8279665063424</v>
       </c>
       <c r="E78">
-        <v>-5.77286904236772</v>
+        <v>-6.230222274772387</v>
       </c>
       <c r="F78">
-        <v>1.638597309292207</v>
+        <v>1.29251163929714</v>
       </c>
       <c r="G78">
-        <v>-2.516091903061839</v>
+        <v>-1.727999984710637</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-16.44648432443203</v>
       </c>
       <c r="E79">
-        <v>-6.280302668823214</v>
+        <v>-8.198627657108485</v>
       </c>
       <c r="F79">
-        <v>1.416759703187026</v>
+        <v>0.9881106927023547</v>
       </c>
       <c r="G79">
-        <v>-2.532724083851138</v>
+        <v>-3.092176485078115</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-16.07404366242277</v>
       </c>
       <c r="E80">
-        <v>-7.918306059085674</v>
+        <v>-6.825784533891155</v>
       </c>
       <c r="F80">
-        <v>1.453875435021265</v>
+        <v>1.126403060650358</v>
       </c>
       <c r="G80">
-        <v>-1.973010149526558</v>
+        <v>-1.547128329172555</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.72405712250875</v>
       </c>
       <c r="E81">
-        <v>-8.52539781302797</v>
+        <v>-8.878048197901292</v>
       </c>
       <c r="F81">
-        <v>1.458344653114635</v>
+        <v>1.091911529518002</v>
       </c>
       <c r="G81">
-        <v>-2.322113797733783</v>
+        <v>-0.9342834494882127</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.4094411897255</v>
       </c>
       <c r="E82">
-        <v>-8.695211059841601</v>
+        <v>-10.02355739745956</v>
       </c>
       <c r="F82">
-        <v>1.137333798878721</v>
+        <v>0.8245297086966141</v>
       </c>
       <c r="G82">
-        <v>-1.838300740988074</v>
+        <v>-1.581829467515196</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.13590458291676</v>
       </c>
       <c r="E83">
-        <v>-9.613970508887801</v>
+        <v>-9.732109338799905</v>
       </c>
       <c r="F83">
-        <v>1.022249057415567</v>
+        <v>0.7043834431277159</v>
       </c>
       <c r="G83">
-        <v>-1.508143344902098</v>
+        <v>-1.346962814231602</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.90170936987834</v>
       </c>
       <c r="E84">
-        <v>-10.02889646831461</v>
+        <v>-11.88302128059313</v>
       </c>
       <c r="F84">
-        <v>1.20877635643011</v>
+        <v>0.6634604822727607</v>
       </c>
       <c r="G84">
-        <v>-1.412031586805977</v>
+        <v>-1.176628625145021</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.70640131299464</v>
       </c>
       <c r="E85">
-        <v>-12.96605565274158</v>
+        <v>-12.42973489059116</v>
       </c>
       <c r="F85">
-        <v>1.082553411263671</v>
+        <v>0.4373832954319486</v>
       </c>
       <c r="G85">
-        <v>-1.434102993916298</v>
+        <v>-1.240290415865205</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.54738949715232</v>
       </c>
       <c r="E86">
-        <v>-13.35472099139791</v>
+        <v>-14.29108261891192</v>
       </c>
       <c r="F86">
-        <v>0.9059749528099187</v>
+        <v>0.4510807678945844</v>
       </c>
       <c r="G86">
-        <v>-1.311665777691892</v>
+        <v>0.1283255260704351</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.41654553519898</v>
       </c>
       <c r="E87">
-        <v>-14.69850489690802</v>
+        <v>-15.17220139200637</v>
       </c>
       <c r="F87">
-        <v>0.8838711693481303</v>
+        <v>0.6017751368663942</v>
       </c>
       <c r="G87">
-        <v>-0.1464994118721625</v>
+        <v>-0.8846550613089983</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.30981021869169</v>
       </c>
       <c r="E88">
-        <v>-15.26400261708986</v>
+        <v>-16.07286053044391</v>
       </c>
       <c r="F88">
-        <v>0.6238171557974803</v>
+        <v>0.5335609638236285</v>
       </c>
       <c r="G88">
-        <v>-0.4697179045078263</v>
+        <v>0.09491881103364956</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.22644254199052</v>
       </c>
       <c r="E89">
-        <v>-17.90793405257217</v>
+        <v>-18.08990625209639</v>
       </c>
       <c r="F89">
-        <v>0.5563053563282122</v>
+        <v>0.3480583225363752</v>
       </c>
       <c r="G89">
-        <v>0.1272893253166432</v>
+        <v>-0.5325321955699578</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.16171576924655</v>
       </c>
       <c r="E90">
-        <v>-19.3072279924683</v>
+        <v>-19.77056786751111</v>
       </c>
       <c r="F90">
-        <v>0.2301300371020499</v>
+        <v>0.1680075888630221</v>
       </c>
       <c r="G90">
-        <v>-0.4770342101496156</v>
+        <v>0.2978089049534235</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.11764247670399</v>
       </c>
       <c r="E91">
-        <v>-20.74196629842247</v>
+        <v>-20.90586535818208</v>
       </c>
       <c r="F91">
-        <v>0.2670652264619287</v>
+        <v>-0.08942539139757549</v>
       </c>
       <c r="G91">
-        <v>0.5173775273000457</v>
+        <v>-0.2801030982005298</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-14.10253912136613</v>
       </c>
       <c r="E92">
-        <v>-22.11886240587667</v>
+        <v>-23.26726530032584</v>
       </c>
       <c r="F92">
-        <v>0.3593097612126148</v>
+        <v>0.02164623927585472</v>
       </c>
       <c r="G92">
-        <v>-0.2717704550781842</v>
+        <v>0.7460137338787317</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-14.11544964423128</v>
       </c>
       <c r="E93">
-        <v>-26.05822270141518</v>
+        <v>-27.07684858775253</v>
       </c>
       <c r="F93">
-        <v>-0.1780764974261294</v>
+        <v>-0.3290971098165197</v>
       </c>
       <c r="G93">
-        <v>0.808202331833941</v>
+        <v>0.5158811607162952</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.15472891739644</v>
       </c>
       <c r="E94">
-        <v>-27.23786753804327</v>
+        <v>-29.0113492851932</v>
       </c>
       <c r="F94">
-        <v>-0.4127983430063676</v>
+        <v>-0.2966295548440956</v>
       </c>
       <c r="G94">
-        <v>0.5641654674065655</v>
+        <v>-0.3657303585737791</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.2208772764708</v>
       </c>
       <c r="E95">
-        <v>-29.65395786077766</v>
+        <v>-29.77374731946556</v>
       </c>
       <c r="F95">
-        <v>-0.6541091970477917</v>
+        <v>-0.1992427269859776</v>
       </c>
       <c r="G95">
-        <v>-0.2357583407019922</v>
+        <v>0.3012684250419619</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.29804817840922</v>
       </c>
       <c r="E96">
-        <v>-31.74288405035389</v>
+        <v>-32.62585044084346</v>
       </c>
       <c r="F96">
-        <v>-0.7784158580565493</v>
+        <v>-0.343165961316326</v>
       </c>
       <c r="G96">
-        <v>-0.4087211029467547</v>
+        <v>0.6105462104117547</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-14.37394018962763</v>
       </c>
       <c r="E97">
-        <v>-33.9146813142705</v>
+        <v>-35.32061399706188</v>
       </c>
       <c r="F97">
-        <v>-0.8330172869031552</v>
+        <v>-0.7674193960326956</v>
       </c>
       <c r="G97">
-        <v>-0.6922163596567035</v>
+        <v>0.04376095081529191</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-14.43588694961876</v>
       </c>
       <c r="E98">
-        <v>-38.04567983710261</v>
+        <v>-38.08348353811864</v>
       </c>
       <c r="F98">
-        <v>-1.234913545211266</v>
+        <v>-0.6872561618579394</v>
       </c>
       <c r="G98">
-        <v>-0.03171286638901261</v>
+        <v>-0.8974304565450458</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.46920301401714</v>
       </c>
       <c r="E99">
-        <v>-39.51234841328486</v>
+        <v>-41.44422938851209</v>
       </c>
       <c r="F99">
-        <v>-1.416083167113877</v>
+        <v>-0.8417926013806052</v>
       </c>
       <c r="G99">
-        <v>-0.6315208177397056</v>
+        <v>-0.7172308417514366</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-14.45277756872045</v>
       </c>
       <c r="E100">
-        <v>-43.33200529114162</v>
+        <v>-43.03593366052013</v>
       </c>
       <c r="F100">
-        <v>-1.43949113239703</v>
+        <v>-1.241904814974973</v>
       </c>
       <c r="G100">
-        <v>-0.652559334641774</v>
+        <v>-1.443792960709745</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-14.39450544281278</v>
       </c>
       <c r="E101">
-        <v>-45.42347648311016</v>
+        <v>-46.51135179397281</v>
       </c>
       <c r="F101">
-        <v>-1.88328116328626</v>
+        <v>-0.9161523452282335</v>
       </c>
       <c r="G101">
-        <v>-1.680864437322494</v>
+        <v>-1.170752406812814</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.26381636936056</v>
       </c>
       <c r="E102">
-        <v>-48.11059371096662</v>
+        <v>-48.46223198189923</v>
       </c>
       <c r="F102">
-        <v>-2.030423279889739</v>
+        <v>-1.347853157011957</v>
       </c>
       <c r="G102">
-        <v>-1.189639069114356</v>
+        <v>-0.9933568240909677</v>
       </c>
     </row>
   </sheetData>
